--- a/data.mn/public/datasets/mrpam-petroleum-production.xlsx
+++ b/data.mn/public/datasets/mrpam-petroleum-production.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Өгөгдөл MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,955 +414,888 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>Exports</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>production_barrels</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>export_barrels</t>
+          <t>Production</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2021</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>518973</v>
       </c>
       <c r="C2" t="n">
         <v>527156</v>
       </c>
-      <c r="D2" t="n">
-        <v>518973</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2021</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>435559</v>
       </c>
       <c r="C3" t="n">
         <v>469647</v>
       </c>
-      <c r="D3" t="n">
-        <v>435559</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2021</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>466990</v>
       </c>
       <c r="C4" t="n">
         <v>511305</v>
       </c>
-      <c r="D4" t="n">
-        <v>466990</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2021</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>468414</v>
       </c>
       <c r="C5" t="n">
         <v>496623</v>
       </c>
-      <c r="D5" t="n">
-        <v>468414</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2021</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>487367</v>
       </c>
       <c r="C6" t="n">
         <v>504353</v>
       </c>
-      <c r="D6" t="n">
-        <v>487367</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2021</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>480475</v>
       </c>
       <c r="C7" t="n">
         <v>482461</v>
       </c>
-      <c r="D7" t="n">
-        <v>480475</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2021</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>425415</v>
       </c>
       <c r="C8" t="n">
         <v>501112</v>
       </c>
-      <c r="D8" t="n">
-        <v>425415</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2021</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>341637</v>
       </c>
       <c r="C9" t="n">
         <v>414776</v>
       </c>
-      <c r="D9" t="n">
-        <v>341637</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2021</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>81278</v>
       </c>
       <c r="C10" t="n">
         <v>51634</v>
       </c>
-      <c r="D10" t="n">
-        <v>81278</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>2021</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>329572</v>
       </c>
       <c r="C11" t="n">
         <v>284781</v>
       </c>
-      <c r="D11" t="n">
-        <v>329572</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>2021</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>312552</v>
       </c>
       <c r="C12" t="n">
         <v>389883</v>
       </c>
-      <c r="D12" t="n">
-        <v>312552</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>33623</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>17544</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>9921</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>9257</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>1001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>1290</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>2022</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>114102</v>
       </c>
       <c r="C19" t="n">
         <v>38184</v>
       </c>
-      <c r="D19" t="n">
-        <v>114102</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>2022</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>359232</v>
       </c>
       <c r="C20" t="n">
         <v>351008</v>
       </c>
-      <c r="D20" t="n">
-        <v>359232</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>2022</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>492619</v>
       </c>
       <c r="C21" t="n">
         <v>457301</v>
       </c>
-      <c r="D21" t="n">
-        <v>492619</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>2022</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>428311</v>
       </c>
       <c r="C22" t="n">
         <v>424986</v>
       </c>
-      <c r="D22" t="n">
-        <v>428311</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>2022</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>364645</v>
       </c>
       <c r="C23" t="n">
         <v>417283</v>
       </c>
-      <c r="D23" t="n">
-        <v>364645</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>2022</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>432823</v>
       </c>
       <c r="C24" t="n">
         <v>410196</v>
       </c>
-      <c r="D24" t="n">
-        <v>432823</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2022</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>414179</v>
       </c>
       <c r="C25" t="n">
         <v>428119</v>
       </c>
-      <c r="D25" t="n">
-        <v>414179</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>2023</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>393310</v>
       </c>
       <c r="C26" t="n">
         <v>430818</v>
       </c>
-      <c r="D26" t="n">
-        <v>393310</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>2023</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>368363</v>
       </c>
       <c r="C27" t="n">
         <v>372459</v>
       </c>
-      <c r="D27" t="n">
-        <v>368363</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>2023</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>418535</v>
       </c>
       <c r="C28" t="n">
         <v>402959</v>
       </c>
-      <c r="D28" t="n">
-        <v>418535</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>2023</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>394184</v>
       </c>
       <c r="C29" t="n">
         <v>404405</v>
       </c>
-      <c r="D29" t="n">
-        <v>394184</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>2023</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>415226</v>
       </c>
       <c r="C30" t="n">
         <v>427315</v>
       </c>
-      <c r="D30" t="n">
-        <v>415226</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>2023</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>395403</v>
       </c>
       <c r="C31" t="n">
         <v>415056</v>
       </c>
-      <c r="D31" t="n">
-        <v>395403</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>2023</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>402896</v>
       </c>
       <c r="C32" t="n">
         <v>422488</v>
       </c>
-      <c r="D32" t="n">
-        <v>402896</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>2023</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>384390</v>
       </c>
       <c r="C33" t="n">
         <v>421268</v>
       </c>
-      <c r="D33" t="n">
-        <v>384390</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>2023</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>385602</v>
       </c>
       <c r="C34" t="n">
         <v>409946</v>
       </c>
-      <c r="D34" t="n">
-        <v>385602</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>2023</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
       </c>
       <c r="B35" t="n">
-        <v>10</v>
+        <v>437777</v>
       </c>
       <c r="C35" t="n">
         <v>411238</v>
       </c>
-      <c r="D35" t="n">
-        <v>437777</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>2023</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>359696</v>
       </c>
       <c r="C36" t="n">
         <v>382824</v>
       </c>
-      <c r="D36" t="n">
-        <v>359696</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>2023</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>376755</v>
       </c>
       <c r="C37" t="n">
         <v>388303</v>
       </c>
-      <c r="D37" t="n">
-        <v>376755</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>2024</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>383253</v>
       </c>
       <c r="C38" t="n">
         <v>372568</v>
       </c>
-      <c r="D38" t="n">
-        <v>383253</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>2024</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>324742</v>
       </c>
       <c r="C39" t="n">
         <v>353716</v>
       </c>
-      <c r="D39" t="n">
-        <v>324742</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>2024</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>354380</v>
       </c>
       <c r="C40" t="n">
         <v>367604</v>
       </c>
-      <c r="D40" t="n">
-        <v>354380</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>2024</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>345206</v>
       </c>
       <c r="C41" t="n">
         <v>353608</v>
       </c>
-      <c r="D41" t="n">
-        <v>345206</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>2024</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>346573</v>
       </c>
       <c r="C42" t="n">
         <v>356826</v>
       </c>
-      <c r="D42" t="n">
-        <v>346573</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>2024</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>335746</v>
       </c>
       <c r="C43" t="n">
         <v>331178</v>
       </c>
-      <c r="D43" t="n">
-        <v>335746</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>2024</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>315416</v>
       </c>
       <c r="C44" t="n">
         <v>337318</v>
       </c>
-      <c r="D44" t="n">
-        <v>315416</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>2024</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>358505</v>
       </c>
       <c r="C45" t="n">
         <v>350564</v>
       </c>
-      <c r="D45" t="n">
-        <v>358505</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>2024</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>336406</v>
       </c>
       <c r="C46" t="n">
         <v>331286</v>
       </c>
-      <c r="D46" t="n">
-        <v>336406</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>2024</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>344649</v>
       </c>
       <c r="C47" t="n">
         <v>346663</v>
       </c>
-      <c r="D47" t="n">
-        <v>344649</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>2024</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>328206</v>
       </c>
       <c r="C48" t="n">
         <v>342334</v>
       </c>
-      <c r="D48" t="n">
-        <v>328206</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>2024</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>294567</v>
       </c>
       <c r="C49" t="n">
         <v>344625</v>
       </c>
-      <c r="D49" t="n">
-        <v>294567</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>2025</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>284063</v>
       </c>
       <c r="C50" t="n">
         <v>317091</v>
       </c>
-      <c r="D50" t="n">
-        <v>284063</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>2025</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>311504</v>
       </c>
       <c r="C51" t="n">
         <v>298844</v>
       </c>
-      <c r="D51" t="n">
-        <v>311504</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>2025</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>322496</v>
       </c>
       <c r="C52" t="n">
         <v>327015</v>
       </c>
-      <c r="D52" t="n">
-        <v>322496</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>2025</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>255271</v>
       </c>
       <c r="C53" t="n">
         <v>308528</v>
       </c>
-      <c r="D53" t="n">
-        <v>255271</v>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>2025</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>283159</v>
       </c>
       <c r="C54" t="n">
         <v>316317</v>
       </c>
-      <c r="D54" t="n">
-        <v>283159</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>2025</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>346300</v>
       </c>
       <c r="C55" t="n">
         <v>309128</v>
       </c>
-      <c r="D55" t="n">
-        <v>346300</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>2025</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>296975</v>
       </c>
       <c r="C56" t="n">
         <v>311758</v>
       </c>
-      <c r="D56" t="n">
-        <v>296975</v>
-      </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>2025</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>298486</v>
       </c>
       <c r="C57" t="n">
         <v>306600</v>
       </c>
-      <c r="D57" t="n">
-        <v>298486</v>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>2025</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>272993</v>
       </c>
       <c r="C58" t="n">
         <v>304692</v>
       </c>
-      <c r="D58" t="n">
-        <v>272993</v>
-      </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>2025</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>315945</v>
       </c>
       <c r="C59" t="n">
         <v>322155</v>
       </c>
-      <c r="D59" t="n">
-        <v>315945</v>
-      </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>2025</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>273827</v>
       </c>
       <c r="C60" t="n">
         <v>312569</v>
       </c>
-      <c r="D60" t="n">
-        <v>273827</v>
-      </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>271712</v>
       </c>
       <c r="C61" t="n">
         <v>322625</v>
       </c>
-      <c r="D61" t="n">
-        <v>271712</v>
-      </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>2026</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>282829</v>
       </c>
       <c r="C62" t="n">
         <v>313128</v>
       </c>
-      <c r="D62" t="n">
-        <v>282829</v>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>2026</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>236574</v>
       </c>
       <c r="C63" t="n">
         <v>271742</v>
       </c>
-      <c r="D63" t="n">
-        <v>236574</v>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>2026</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>358416</v>
       </c>
       <c r="C64" t="n">
         <v>301787</v>
       </c>
-      <c r="D64" t="n">
-        <v>358416</v>
-      </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>2026</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>271457</v>
       </c>
       <c r="C65" t="n">
         <v>293874</v>
       </c>
-      <c r="D65" t="n">
-        <v>271457</v>
-      </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>2026</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>280061</v>
       </c>
       <c r="C66" t="n">
         <v>297409</v>
       </c>
-      <c r="D66" t="n">
-        <v>280061</v>
-      </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>2026</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>287125</v>
       </c>
       <c r="C67" t="n">
         <v>280726</v>
       </c>
-      <c r="D67" t="n">
-        <v>287125</v>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>2026</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>234735</v>
       </c>
       <c r="C68" t="n">
         <v>299729</v>
-      </c>
-      <c r="D68" t="n">
-        <v>234735</v>
       </c>
     </row>
   </sheetData>
@@ -1376,954 +1309,887 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>он</t>
+          <t>сар</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>сар</t>
+          <t>Олборлолт</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>олборлолт_баррель</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>экспорт_баррель</t>
+          <t>Экспорт</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2021</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>527156</v>
       </c>
       <c r="C2" t="n">
-        <v>527156</v>
-      </c>
-      <c r="D2" t="n">
         <v>518973</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2021</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>469647</v>
       </c>
       <c r="C3" t="n">
-        <v>469647</v>
-      </c>
-      <c r="D3" t="n">
         <v>435559</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2021</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>511305</v>
       </c>
       <c r="C4" t="n">
-        <v>511305</v>
-      </c>
-      <c r="D4" t="n">
         <v>466990</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2021</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>496623</v>
       </c>
       <c r="C5" t="n">
-        <v>496623</v>
-      </c>
-      <c r="D5" t="n">
         <v>468414</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2021</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>504353</v>
       </c>
       <c r="C6" t="n">
-        <v>504353</v>
-      </c>
-      <c r="D6" t="n">
         <v>487367</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2021</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>482461</v>
       </c>
       <c r="C7" t="n">
-        <v>482461</v>
-      </c>
-      <c r="D7" t="n">
         <v>480475</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2021</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>501112</v>
       </c>
       <c r="C8" t="n">
-        <v>501112</v>
-      </c>
-      <c r="D8" t="n">
         <v>425415</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2021</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>414776</v>
       </c>
       <c r="C9" t="n">
-        <v>414776</v>
-      </c>
-      <c r="D9" t="n">
         <v>341637</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2021</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>51634</v>
       </c>
       <c r="C10" t="n">
-        <v>51634</v>
-      </c>
-      <c r="D10" t="n">
         <v>81278</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>2021</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>284781</v>
       </c>
       <c r="C11" t="n">
-        <v>284781</v>
-      </c>
-      <c r="D11" t="n">
         <v>329572</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>2021</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>389883</v>
       </c>
       <c r="C12" t="n">
-        <v>389883</v>
-      </c>
-      <c r="D12" t="n">
         <v>312552</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2021</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="n">
         <v>33623</v>
       </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>2022</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
         <v>17544</v>
       </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>2022</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
         <v>9921</v>
       </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>2022</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
         <v>9257</v>
       </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>2022</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" t="n">
         <v>1001</v>
       </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>2022</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="n">
         <v>1290</v>
       </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>2022</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>38184</v>
       </c>
       <c r="C19" t="n">
-        <v>38184</v>
-      </c>
-      <c r="D19" t="n">
         <v>114102</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>2022</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>351008</v>
       </c>
       <c r="C20" t="n">
-        <v>351008</v>
-      </c>
-      <c r="D20" t="n">
         <v>359232</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>2022</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>457301</v>
       </c>
       <c r="C21" t="n">
-        <v>457301</v>
-      </c>
-      <c r="D21" t="n">
         <v>492619</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>2022</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>424986</v>
       </c>
       <c r="C22" t="n">
-        <v>424986</v>
-      </c>
-      <c r="D22" t="n">
         <v>428311</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>2022</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>417283</v>
       </c>
       <c r="C23" t="n">
-        <v>417283</v>
-      </c>
-      <c r="D23" t="n">
         <v>364645</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>2022</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>410196</v>
       </c>
       <c r="C24" t="n">
-        <v>410196</v>
-      </c>
-      <c r="D24" t="n">
         <v>432823</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2022</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>428119</v>
       </c>
       <c r="C25" t="n">
-        <v>428119</v>
-      </c>
-      <c r="D25" t="n">
         <v>414179</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>2023</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>430818</v>
       </c>
       <c r="C26" t="n">
-        <v>430818</v>
-      </c>
-      <c r="D26" t="n">
         <v>393310</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>2023</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>372459</v>
       </c>
       <c r="C27" t="n">
-        <v>372459</v>
-      </c>
-      <c r="D27" t="n">
         <v>368363</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>2023</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>402959</v>
       </c>
       <c r="C28" t="n">
-        <v>402959</v>
-      </c>
-      <c r="D28" t="n">
         <v>418535</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>2023</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>404405</v>
       </c>
       <c r="C29" t="n">
-        <v>404405</v>
-      </c>
-      <c r="D29" t="n">
         <v>394184</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>2023</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>427315</v>
       </c>
       <c r="C30" t="n">
-        <v>427315</v>
-      </c>
-      <c r="D30" t="n">
         <v>415226</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>2023</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>415056</v>
       </c>
       <c r="C31" t="n">
-        <v>415056</v>
-      </c>
-      <c r="D31" t="n">
         <v>395403</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>2023</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>422488</v>
       </c>
       <c r="C32" t="n">
-        <v>422488</v>
-      </c>
-      <c r="D32" t="n">
         <v>402896</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>2023</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>421268</v>
       </c>
       <c r="C33" t="n">
-        <v>421268</v>
-      </c>
-      <c r="D33" t="n">
         <v>384390</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>2023</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>409946</v>
       </c>
       <c r="C34" t="n">
-        <v>409946</v>
-      </c>
-      <c r="D34" t="n">
         <v>385602</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>2023</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
       </c>
       <c r="B35" t="n">
-        <v>10</v>
+        <v>411238</v>
       </c>
       <c r="C35" t="n">
-        <v>411238</v>
-      </c>
-      <c r="D35" t="n">
         <v>437777</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>2023</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>382824</v>
       </c>
       <c r="C36" t="n">
-        <v>382824</v>
-      </c>
-      <c r="D36" t="n">
         <v>359696</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>2023</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>388303</v>
       </c>
       <c r="C37" t="n">
-        <v>388303</v>
-      </c>
-      <c r="D37" t="n">
         <v>376755</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>2024</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>372568</v>
       </c>
       <c r="C38" t="n">
-        <v>372568</v>
-      </c>
-      <c r="D38" t="n">
         <v>383253</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>2024</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>353716</v>
       </c>
       <c r="C39" t="n">
-        <v>353716</v>
-      </c>
-      <c r="D39" t="n">
         <v>324742</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>2024</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>367604</v>
       </c>
       <c r="C40" t="n">
-        <v>367604</v>
-      </c>
-      <c r="D40" t="n">
         <v>354380</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>2024</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>353608</v>
       </c>
       <c r="C41" t="n">
-        <v>353608</v>
-      </c>
-      <c r="D41" t="n">
         <v>345206</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>2024</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>356826</v>
       </c>
       <c r="C42" t="n">
-        <v>356826</v>
-      </c>
-      <c r="D42" t="n">
         <v>346573</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>2024</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>331178</v>
       </c>
       <c r="C43" t="n">
-        <v>331178</v>
-      </c>
-      <c r="D43" t="n">
         <v>335746</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>2024</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>337318</v>
       </c>
       <c r="C44" t="n">
-        <v>337318</v>
-      </c>
-      <c r="D44" t="n">
         <v>315416</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>2024</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>350564</v>
       </c>
       <c r="C45" t="n">
-        <v>350564</v>
-      </c>
-      <c r="D45" t="n">
         <v>358505</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>2024</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>331286</v>
       </c>
       <c r="C46" t="n">
-        <v>331286</v>
-      </c>
-      <c r="D46" t="n">
         <v>336406</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>2024</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>346663</v>
       </c>
       <c r="C47" t="n">
-        <v>346663</v>
-      </c>
-      <c r="D47" t="n">
         <v>344649</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>2024</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>342334</v>
       </c>
       <c r="C48" t="n">
-        <v>342334</v>
-      </c>
-      <c r="D48" t="n">
         <v>328206</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>2024</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>344625</v>
       </c>
       <c r="C49" t="n">
-        <v>344625</v>
-      </c>
-      <c r="D49" t="n">
         <v>294567</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>2025</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>317091</v>
       </c>
       <c r="C50" t="n">
-        <v>317091</v>
-      </c>
-      <c r="D50" t="n">
         <v>284063</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>2025</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>298844</v>
       </c>
       <c r="C51" t="n">
-        <v>298844</v>
-      </c>
-      <c r="D51" t="n">
         <v>311504</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>2025</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>327015</v>
       </c>
       <c r="C52" t="n">
-        <v>327015</v>
-      </c>
-      <c r="D52" t="n">
         <v>322496</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>2025</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>308528</v>
       </c>
       <c r="C53" t="n">
-        <v>308528</v>
-      </c>
-      <c r="D53" t="n">
         <v>255271</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>2025</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>316317</v>
       </c>
       <c r="C54" t="n">
-        <v>316317</v>
-      </c>
-      <c r="D54" t="n">
         <v>283159</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>2025</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>309128</v>
       </c>
       <c r="C55" t="n">
-        <v>309128</v>
-      </c>
-      <c r="D55" t="n">
         <v>346300</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>2025</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>311758</v>
       </c>
       <c r="C56" t="n">
-        <v>311758</v>
-      </c>
-      <c r="D56" t="n">
         <v>296975</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>2025</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>306600</v>
       </c>
       <c r="C57" t="n">
-        <v>306600</v>
-      </c>
-      <c r="D57" t="n">
         <v>298486</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>2025</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>304692</v>
       </c>
       <c r="C58" t="n">
-        <v>304692</v>
-      </c>
-      <c r="D58" t="n">
         <v>272993</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>2025</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>322155</v>
       </c>
       <c r="C59" t="n">
-        <v>322155</v>
-      </c>
-      <c r="D59" t="n">
         <v>315945</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>2025</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>312569</v>
       </c>
       <c r="C60" t="n">
-        <v>312569</v>
-      </c>
-      <c r="D60" t="n">
         <v>273827</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>322625</v>
       </c>
       <c r="C61" t="n">
-        <v>322625</v>
-      </c>
-      <c r="D61" t="n">
         <v>271712</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>2026</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>313128</v>
       </c>
       <c r="C62" t="n">
-        <v>313128</v>
-      </c>
-      <c r="D62" t="n">
         <v>282829</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>2026</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>271742</v>
       </c>
       <c r="C63" t="n">
-        <v>271742</v>
-      </c>
-      <c r="D63" t="n">
         <v>236574</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>2026</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>301787</v>
       </c>
       <c r="C64" t="n">
-        <v>301787</v>
-      </c>
-      <c r="D64" t="n">
         <v>358416</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>2026</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>293874</v>
       </c>
       <c r="C65" t="n">
-        <v>293874</v>
-      </c>
-      <c r="D65" t="n">
         <v>271457</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>2026</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>297409</v>
       </c>
       <c r="C66" t="n">
-        <v>297409</v>
-      </c>
-      <c r="D66" t="n">
         <v>280061</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>2026</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>280726</v>
       </c>
       <c r="C67" t="n">
-        <v>280726</v>
-      </c>
-      <c r="D67" t="n">
         <v>287125</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>2026</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>299729</v>
       </c>
       <c r="C68" t="n">
-        <v>299729</v>
-      </c>
-      <c r="D68" t="n">
         <v>234735</v>
       </c>
     </row>

--- a/data.mn/public/datasets/mrpam-petroleum-production.xlsx
+++ b/data.mn/public/datasets/mrpam-petroleum-production.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1296,6 +1296,32 @@
       </c>
       <c r="C68" t="n">
         <v>299729</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>269463</v>
+      </c>
+      <c r="C69" t="n">
+        <v>295959</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>258476</v>
+      </c>
+      <c r="C70" t="n">
+        <v>281965</v>
       </c>
     </row>
   </sheetData>
@@ -1309,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2193,6 +2219,32 @@
         <v>234735</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>295959</v>
+      </c>
+      <c r="C69" t="n">
+        <v>269463</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>281965</v>
+      </c>
+      <c r="C70" t="n">
+        <v>258476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
